--- a/Data_resultados/openai_manipulative_design.xlsx
+++ b/Data_resultados/openai_manipulative_design.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.trello.com/</t>
+          <t>https://www.shopee.com.br/</t>
         </is>
       </c>
       <c r="B2" t="b">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/</t>
+          <t>https://www.github.com/</t>
         </is>
       </c>
       <c r="B3" t="b">
